--- a/assets/xlsx/주별투자수익_2026-06-08_2026-08-27.xlsx
+++ b/assets/xlsx/주별투자수익_2026-06-08_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>203249597</v>
+        <v>183909378</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>203140658</v>
+        <v>183843260</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>108939</v>
+        <v>66118</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.77</v>
+        <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0706</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>199873197</v>
+        <v>178495131</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>199765126</v>
+        <v>178432228</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>108071</v>
+        <v>62903</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0416</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>208433080</v>
+        <v>189278037</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>208323526</v>
+        <v>189212006</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>109554</v>
+        <v>66031</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>199478189</v>
+        <v>178871652</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>199366184</v>
+        <v>178802095</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>112005</v>
+        <v>69557</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0747</v>
+        <v>0.0468</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>208063589</v>
+        <v>188576698</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>207943441</v>
+        <v>188497009</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>120148</v>
+        <v>79689</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0781</v>
+        <v>0.0522</v>
       </c>
     </row>
     <row r="9">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>198200577</v>
+        <v>176605091</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>198089834</v>
+        <v>176539107</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>110743</v>
+        <v>65984</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0747</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="10">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>205476846</v>
+        <v>186377041</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>205362869</v>
+        <v>186303876</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>113977</v>
+        <v>73165</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0737</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>204126881</v>
+        <v>183683667</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>204012168</v>
+        <v>183612457</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>114713</v>
+        <v>71210</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2.72</v>
+        <v>3.01</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0471</v>
       </c>
     </row>
     <row r="12">
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>202824401</v>
+        <v>182300943</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>202702969</v>
+        <v>182219113</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>121432</v>
+        <v>81830</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.0818</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="13">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>200513829</v>
+        <v>180356267</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>200405709</v>
+        <v>180292609</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>108120</v>
+        <v>63658</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.0711</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="14">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>204072049</v>
+        <v>182978146</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>203958761</v>
+        <v>182908498</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>113288</v>
+        <v>69648</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="15">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>114760241</v>
+        <v>103516828</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>114700927</v>
+        <v>103483283</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>59314</v>
+        <v>33545</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2.81</v>
+        <v>3.12</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.0672</v>
+        <v>0.0379</v>
       </c>
     </row>
     <row r="16">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>2349072476</v>
+        <v>2114948879</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2347772172</v>
+        <v>2114145541</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1300304</v>
+        <v>803338</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.0736</v>
+        <v>0.0457</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/주별투자수익_2026-06-08_2026-08-27.xlsx
+++ b/assets/xlsx/주별투자수익_2026-06-08_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>183909393</v>
+        <v>184045722</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>183843260</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>66118</v>
+        <v>202447</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0429</v>
+        <v>0.1313</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>178495145</v>
+        <v>178628730</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>178432228</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>62903</v>
+        <v>196488</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0416</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>189278046</v>
+        <v>189420375</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>189212006</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>66031</v>
+        <v>208360</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.07</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0415</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>178871654</v>
+        <v>178998992</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>178802095</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>69557</v>
+        <v>196895</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3.04</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0467</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>188576708</v>
+        <v>188704589</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>188497009</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>79689</v>
+        <v>207570</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>2.96</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0522</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="9">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>176605100</v>
+        <v>176733520</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>176539107</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>65984</v>
+        <v>194404</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>3.04</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0449</v>
+        <v>0.1322</v>
       </c>
     </row>
     <row r="10">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>186377050</v>
+        <v>186509042</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>186303876</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>73165</v>
+        <v>205157</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>3.02</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0475</v>
+        <v>0.1332</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>183683693</v>
+        <v>183814675</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>183612457</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>71210</v>
+        <v>202192</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>3.01</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.0471</v>
+        <v>0.1336</v>
       </c>
     </row>
     <row r="12">
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>182300961</v>
+        <v>182419789</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>182219113</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>81830</v>
+        <v>200658</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>2.93</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.056</v>
+        <v>0.1372</v>
       </c>
     </row>
     <row r="13">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>180356275</v>
+        <v>180491152</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>180292609</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>63658</v>
+        <v>198535</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>3.07</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.042</v>
+        <v>0.1309</v>
       </c>
     </row>
     <row r="14">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>182978149</v>
+        <v>183109919</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>182908498</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>69648</v>
+        <v>201418</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>3.04</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.0458</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="15">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>103516848</v>
+        <v>103597259</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>103483283</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>33545</v>
+        <v>113956</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.0379</v>
+        <v>0.1288</v>
       </c>
     </row>
     <row r="16">
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>2114949022</v>
+        <v>2116473764</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>2114145541</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>803338</v>
+        <v>2328080</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>3.03</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.0457</v>
+        <v>0.1325</v>
       </c>
     </row>
   </sheetData>
